--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1108-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1108-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45A657C1-013B-408E-B989-CD76BD134EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DCC898B-783C-4211-930A-562817B02B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{50D7FC28-5022-455E-9514-9551D10BC144}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D2EA80C1-25F7-4C30-A0DC-758A95C2DF53}"/>
   </bookViews>
   <sheets>
     <sheet name="1108-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1622,30 +1622,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25EBE7AF-2822-47A4-8E8D-E5520FAFAC34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C430F4E7-E20B-47D1-B059-2F7FE9A0C9E3}">
   <dimension ref="A1:X71"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1679,7 +1679,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1715,7 +1715,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1835,7 +1835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2023</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2022</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2021</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2020</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2019</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>2018</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2017</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>2016</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>7.24</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2015</v>
       </c>
@@ -4033,7 +4033,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2014</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>2013</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="41">
         <v>2012</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>2011</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="41">
         <v>2010</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>2009</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="41">
         <v>2008</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>2007</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>2006</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="39">
         <v>2005</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="41">
         <v>2004</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="39">
         <v>2003</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="41">
         <v>2002</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>2001</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="41">
         <v>2000</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>1999</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="41">
         <v>1998</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="39">
         <v>1997</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="43">
         <v>1996</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="45"/>
       <c r="B54" s="46"/>
       <c r="C54" s="20" t="s">
@@ -5429,7 +5429,7 @@
       <c r="W54" s="52"/>
       <c r="X54" s="48"/>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <v>1995</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="55"/>
       <c r="B56" s="56"/>
       <c r="C56" s="22" t="s">
@@ -5529,7 +5529,7 @@
       <c r="W56" s="62"/>
       <c r="X56" s="58"/>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="43">
         <v>1994</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="45"/>
       <c r="B58" s="46"/>
       <c r="C58" s="20" t="s">
@@ -5629,7 +5629,7 @@
       <c r="W58" s="52"/>
       <c r="X58" s="48"/>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <v>1993</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="55"/>
       <c r="B60" s="56"/>
       <c r="C60" s="22" t="s">
@@ -5729,7 +5729,7 @@
       <c r="W60" s="62"/>
       <c r="X60" s="58"/>
     </row>
-    <row r="61" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="43">
         <v>1992</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="45"/>
       <c r="B62" s="46"/>
       <c r="C62" s="20" t="s">
@@ -5829,7 +5829,7 @@
       <c r="W62" s="52"/>
       <c r="X62" s="48"/>
     </row>
-    <row r="63" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="53">
         <v>1991</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="55"/>
       <c r="B64" s="56"/>
       <c r="C64" s="22" t="s">
@@ -5929,7 +5929,7 @@
       <c r="W64" s="62"/>
       <c r="X64" s="58"/>
     </row>
-    <row r="65" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="43">
         <v>1990</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="66" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="45"/>
       <c r="B66" s="46"/>
       <c r="C66" s="20" t="s">
@@ -6029,7 +6029,7 @@
       <c r="W66" s="52"/>
       <c r="X66" s="48"/>
     </row>
-    <row r="67" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="39">
         <v>1989</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="41">
         <v>1988</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="39">
         <v>1985</v>
       </c>
@@ -6245,7 +6245,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="41">
         <v>1984</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="39" t="s">
         <v>71</v>
       </c>
